--- a/artfynd/A 60967-2025 artfynd.xlsx
+++ b/artfynd/A 60967-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130862972</v>
+        <v>130862980</v>
       </c>
       <c r="B3" t="n">
-        <v>91796</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,37 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söderåsen Väst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447167</v>
+        <v>447218</v>
       </c>
       <c r="R3" t="n">
-        <v>7042999</v>
+        <v>7042948</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en gammal relativt grov döende stående gran med full längd och 36 cm i brösthöjdsdiameter..</t>
+          <t>På en tydligt gammal gran med nedåthängande grenar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,34 +861,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -908,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130862980</v>
+        <v>130862972</v>
       </c>
       <c r="B4" t="n">
-        <v>79221</v>
+        <v>91796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,34 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Söderåsen Väst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447218</v>
+        <v>447167</v>
       </c>
       <c r="R4" t="n">
-        <v>7042948</v>
+        <v>7042999</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +957,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en tydligt gammal gran med nedåthängande grenar.</t>
+          <t>Flera fruktkroppar i en gammal relativt grov döende stående gran med full längd och 36 cm i brösthöjdsdiameter..</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,8 +966,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130862986</v>
+        <v>130862974</v>
       </c>
       <c r="B5" t="n">
         <v>79221</v>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447285</v>
+        <v>447120</v>
       </c>
       <c r="R5" t="n">
-        <v>7042837</v>
+        <v>7043128</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar i gles mycket luckig gammal granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130862978</v>
+        <v>130862986</v>
       </c>
       <c r="B6" t="n">
         <v>79221</v>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447078</v>
+        <v>447285</v>
       </c>
       <c r="R6" t="n">
-        <v>7043076</v>
+        <v>7042837</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Garnlav på flera granar i gles mycket luckig gammal granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,7 +1214,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130862974</v>
+        <v>130862978</v>
       </c>
       <c r="B7" t="n">
         <v>79221</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447120</v>
+        <v>447078</v>
       </c>
       <c r="R7" t="n">
-        <v>7043128</v>
+        <v>7043076</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130862984</v>
+        <v>130862988</v>
       </c>
       <c r="B13" t="n">
         <v>79221</v>
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447249</v>
+        <v>447308</v>
       </c>
       <c r="R13" t="n">
-        <v>7042828</v>
+        <v>7042764</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130862988</v>
+        <v>130862984</v>
       </c>
       <c r="B14" t="n">
         <v>79221</v>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447308</v>
+        <v>447249</v>
       </c>
       <c r="R14" t="n">
-        <v>7042764</v>
+        <v>7042828</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,6 +2143,1835 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130865716</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91796</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Söderåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>447126</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7043116</v>
+      </c>
+      <c r="S15" t="n">
+        <v>11</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130865706</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Söderåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>447322</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7042723</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130865707</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Söderåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>447282</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7042740</v>
+      </c>
+      <c r="S17" t="n">
+        <v>9</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130865719</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Söderåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>447105</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7043139</v>
+      </c>
+      <c r="S18" t="n">
+        <v>11</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130865717</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Söderåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>447119</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7043125</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130865702</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Söderåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>447402</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7042777</v>
+      </c>
+      <c r="S20" t="n">
+        <v>6</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130865701</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Söderåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>447439</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7042775</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130865710</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Söderåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>447169</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7042897</v>
+      </c>
+      <c r="S22" t="n">
+        <v>6</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130865715</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91776</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Söderåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>447136</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7043068</v>
+      </c>
+      <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130865714</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Söderåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>447144</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7043043</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130865712</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Söderåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>447165</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7043032</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130865713</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91772</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Söderåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>447144</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7043043</v>
+      </c>
+      <c r="S26" t="n">
+        <v>13</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130865703</v>
+      </c>
+      <c r="B27" t="n">
+        <v>89169</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>510</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Söderåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>447410</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7042768</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130865708</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Söderåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>447180</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7042900</v>
+      </c>
+      <c r="S28" t="n">
+        <v>13</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130865720</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57044</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Söderåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>447216</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7043049</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Överflygande över vägen</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130865711</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91772</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Söderåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>447138</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7042959</v>
+      </c>
+      <c r="S30" t="n">
+        <v>12</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130865704</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Söderåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>447376</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7042794</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60967-2025 artfynd.xlsx
+++ b/artfynd/A 60967-2025 artfynd.xlsx
@@ -3217,10 +3217,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130865712</v>
+        <v>130865713</v>
       </c>
       <c r="B25" t="n">
-        <v>79221</v>
+        <v>91772</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3228,21 +3228,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3252,13 +3252,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447165</v>
+        <v>447144</v>
       </c>
       <c r="R25" t="n">
-        <v>7043032</v>
+        <v>7043043</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3324,10 +3324,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130865713</v>
+        <v>130865703</v>
       </c>
       <c r="B26" t="n">
-        <v>91772</v>
+        <v>89169</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3335,21 +3335,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3359,13 +3359,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447144</v>
+        <v>447410</v>
       </c>
       <c r="R26" t="n">
-        <v>7043043</v>
+        <v>7042768</v>
       </c>
       <c r="S26" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3431,10 +3431,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130865703</v>
+        <v>130865712</v>
       </c>
       <c r="B27" t="n">
-        <v>89169</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3466,13 +3466,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447410</v>
+        <v>447165</v>
       </c>
       <c r="R27" t="n">
-        <v>7042768</v>
+        <v>7043032</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 60967-2025 artfynd.xlsx
+++ b/artfynd/A 60967-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130862980</v>
+        <v>130862972</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>91829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söderåsen Väst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447218</v>
+        <v>447167</v>
       </c>
       <c r="R3" t="n">
-        <v>7042948</v>
+        <v>7042999</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +855,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På en tydligt gammal gran med nedåthängande grenar.</t>
+          <t>Flera fruktkroppar i en gammal relativt grov döende stående gran med full längd och 36 cm i brösthöjdsdiameter..</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,8 +864,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -879,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130862972</v>
+        <v>130862980</v>
       </c>
       <c r="B4" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,37 +919,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Söderåsen Väst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447167</v>
+        <v>447218</v>
       </c>
       <c r="R4" t="n">
-        <v>7042999</v>
+        <v>7042948</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +983,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en gammal relativt grov döende stående gran med full längd och 36 cm i brösthöjdsdiameter..</t>
+          <t>På en tydligt gammal gran med nedåthängande grenar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,34 +992,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1112,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130862986</v>
+        <v>130862978</v>
       </c>
       <c r="B6" t="n">
         <v>79244</v>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447285</v>
+        <v>447078</v>
       </c>
       <c r="R6" t="n">
-        <v>7042837</v>
+        <v>7043076</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar i gles mycket luckig gammal granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,7 +1214,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130862978</v>
+        <v>130862986</v>
       </c>
       <c r="B7" t="n">
         <v>79244</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447078</v>
+        <v>447285</v>
       </c>
       <c r="R7" t="n">
-        <v>7043076</v>
+        <v>7042837</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Garnlav på flera granar i gles mycket luckig gammal granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1942,7 +1942,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130862988</v>
+        <v>130862984</v>
       </c>
       <c r="B13" t="n">
         <v>79244</v>
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447308</v>
+        <v>447249</v>
       </c>
       <c r="R13" t="n">
-        <v>7042764</v>
+        <v>7042828</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130862984</v>
+        <v>130862988</v>
       </c>
       <c r="B14" t="n">
         <v>79244</v>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447249</v>
+        <v>447308</v>
       </c>
       <c r="R14" t="n">
-        <v>7042828</v>
+        <v>7042764</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130865706</v>
+        <v>130865719</v>
       </c>
       <c r="B16" t="n">
         <v>79244</v>
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447322</v>
+        <v>447105</v>
       </c>
       <c r="R16" t="n">
-        <v>7042723</v>
+        <v>7043139</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2329,7 +2329,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2463,7 +2468,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130865719</v>
+        <v>130865706</v>
       </c>
       <c r="B18" t="n">
         <v>79244</v>
@@ -2498,13 +2503,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447105</v>
+        <v>447322</v>
       </c>
       <c r="R18" t="n">
-        <v>7043139</v>
+        <v>7042723</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2533,7 +2538,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2543,12 +2548,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2896,10 +2896,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130865710</v>
+        <v>130865715</v>
       </c>
       <c r="B22" t="n">
-        <v>79244</v>
+        <v>91809</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2907,21 +2907,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2931,13 +2931,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447169</v>
+        <v>447136</v>
       </c>
       <c r="R22" t="n">
-        <v>7042897</v>
+        <v>7043068</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3003,10 +3003,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130865715</v>
+        <v>130865710</v>
       </c>
       <c r="B23" t="n">
-        <v>91809</v>
+        <v>79244</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3038,13 +3038,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447136</v>
+        <v>447169</v>
       </c>
       <c r="R23" t="n">
-        <v>7043068</v>
+        <v>7042897</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3217,10 +3217,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130865712</v>
+        <v>130865713</v>
       </c>
       <c r="B25" t="n">
-        <v>79244</v>
+        <v>91805</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3228,21 +3228,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3252,13 +3252,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447165</v>
+        <v>447144</v>
       </c>
       <c r="R25" t="n">
-        <v>7043032</v>
+        <v>7043043</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3324,10 +3324,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130865713</v>
+        <v>130865703</v>
       </c>
       <c r="B26" t="n">
-        <v>91805</v>
+        <v>89194</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3335,21 +3335,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3359,13 +3359,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447144</v>
+        <v>447410</v>
       </c>
       <c r="R26" t="n">
-        <v>7043043</v>
+        <v>7042768</v>
       </c>
       <c r="S26" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3431,10 +3431,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130865703</v>
+        <v>130865712</v>
       </c>
       <c r="B27" t="n">
-        <v>89194</v>
+        <v>79244</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3466,13 +3466,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447410</v>
+        <v>447165</v>
       </c>
       <c r="R27" t="n">
-        <v>7042768</v>
+        <v>7043032</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 60967-2025 artfynd.xlsx
+++ b/artfynd/A 60967-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130862972</v>
+        <v>130862980</v>
       </c>
       <c r="B3" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,37 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söderåsen Väst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447167</v>
+        <v>447218</v>
       </c>
       <c r="R3" t="n">
-        <v>7042999</v>
+        <v>7042948</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en gammal relativt grov döende stående gran med full längd och 36 cm i brösthöjdsdiameter..</t>
+          <t>På en tydligt gammal gran med nedåthängande grenar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,34 +861,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -908,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130862980</v>
+        <v>130862972</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>91829</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,34 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Söderåsen Väst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447218</v>
+        <v>447167</v>
       </c>
       <c r="R4" t="n">
-        <v>7042948</v>
+        <v>7042999</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +957,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en tydligt gammal gran med nedåthängande grenar.</t>
+          <t>Flera fruktkroppar i en gammal relativt grov döende stående gran med full längd och 36 cm i brösthöjdsdiameter..</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,8 +966,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1112,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130862978</v>
+        <v>130862986</v>
       </c>
       <c r="B6" t="n">
         <v>79244</v>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447078</v>
+        <v>447285</v>
       </c>
       <c r="R6" t="n">
-        <v>7043076</v>
+        <v>7042837</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Garnlav på flera granar i gles mycket luckig gammal granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,7 +1214,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130862986</v>
+        <v>130862978</v>
       </c>
       <c r="B7" t="n">
         <v>79244</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447285</v>
+        <v>447078</v>
       </c>
       <c r="R7" t="n">
-        <v>7042837</v>
+        <v>7043076</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar i gles mycket luckig gammal granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1942,7 +1942,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130862984</v>
+        <v>130862988</v>
       </c>
       <c r="B13" t="n">
         <v>79244</v>
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447249</v>
+        <v>447308</v>
       </c>
       <c r="R13" t="n">
-        <v>7042828</v>
+        <v>7042764</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130862988</v>
+        <v>130862984</v>
       </c>
       <c r="B14" t="n">
         <v>79244</v>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447308</v>
+        <v>447249</v>
       </c>
       <c r="R14" t="n">
-        <v>7042764</v>
+        <v>7042828</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130865719</v>
+        <v>130865706</v>
       </c>
       <c r="B16" t="n">
         <v>79244</v>
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447105</v>
+        <v>447322</v>
       </c>
       <c r="R16" t="n">
-        <v>7043139</v>
+        <v>7042723</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2329,12 +2329,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2468,7 +2463,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130865706</v>
+        <v>130865719</v>
       </c>
       <c r="B18" t="n">
         <v>79244</v>
@@ -2503,13 +2498,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447322</v>
+        <v>447105</v>
       </c>
       <c r="R18" t="n">
-        <v>7042723</v>
+        <v>7043139</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2538,7 +2533,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2548,7 +2543,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3217,10 +3217,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130865713</v>
+        <v>130865712</v>
       </c>
       <c r="B25" t="n">
-        <v>91805</v>
+        <v>79244</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3228,21 +3228,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3252,13 +3252,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447144</v>
+        <v>447165</v>
       </c>
       <c r="R25" t="n">
-        <v>7043043</v>
+        <v>7043032</v>
       </c>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3324,10 +3324,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130865703</v>
+        <v>130865713</v>
       </c>
       <c r="B26" t="n">
-        <v>89194</v>
+        <v>91805</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3335,21 +3335,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3359,13 +3359,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447410</v>
+        <v>447144</v>
       </c>
       <c r="R26" t="n">
-        <v>7042768</v>
+        <v>7043043</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3431,10 +3431,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130865712</v>
+        <v>130865703</v>
       </c>
       <c r="B27" t="n">
-        <v>79244</v>
+        <v>89194</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3466,13 +3466,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447165</v>
+        <v>447410</v>
       </c>
       <c r="R27" t="n">
-        <v>7043032</v>
+        <v>7042768</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 60967-2025 artfynd.xlsx
+++ b/artfynd/A 60967-2025 artfynd.xlsx
@@ -2356,7 +2356,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130865707</v>
+        <v>130865719</v>
       </c>
       <c r="B17" t="n">
         <v>79244</v>
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447282</v>
+        <v>447105</v>
       </c>
       <c r="R17" t="n">
-        <v>7042740</v>
+        <v>7043139</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2436,7 +2436,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2463,7 +2468,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130865719</v>
+        <v>130865707</v>
       </c>
       <c r="B18" t="n">
         <v>79244</v>
@@ -2498,13 +2503,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447105</v>
+        <v>447282</v>
       </c>
       <c r="R18" t="n">
-        <v>7043139</v>
+        <v>7042740</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2533,7 +2538,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2543,12 +2548,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2896,10 +2896,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130865715</v>
+        <v>130865710</v>
       </c>
       <c r="B22" t="n">
-        <v>91809</v>
+        <v>79244</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2907,21 +2907,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2931,13 +2931,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447136</v>
+        <v>447169</v>
       </c>
       <c r="R22" t="n">
-        <v>7043068</v>
+        <v>7042897</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3003,10 +3003,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130865710</v>
+        <v>130865715</v>
       </c>
       <c r="B23" t="n">
-        <v>79244</v>
+        <v>91809</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3038,13 +3038,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447169</v>
+        <v>447136</v>
       </c>
       <c r="R23" t="n">
-        <v>7042897</v>
+        <v>7043068</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
